--- a/excel-files/MALABON/UPDATED MUZON ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/MALABON/UPDATED MUZON ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Admin officer II\Admin Officer II\MUZON ES\CUSTODIAN\REPORT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_68BF4031F603991C0665D4C296942238B57366DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B62526BF-6984-4755-8BB4-5261D89E2125}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_68BF4031F603991C0665D4C296942238B57366DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{897CF854-9E7F-465B-8967-B7FC121B182F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -675,6 +675,12 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -686,12 +692,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5732,12 +5732,15 @@
     <protectedRange sqref="F93:F97" name="SOURCE_6"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E2:E6 E21:E29 E31:E39 E51:E59 E41:E49 E61:E69 E71:E79 E81:E89 E8:E12 E91:E115" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E99" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F2:F6 F21:F29 F41:F49 F31:F39 F51:F59 F71:F79 F81:F89 F61:F69 F8:F12 F91:F115" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89 E91:E98 E100:E115" xr:uid="{E23E30CB-7D70-46DD-80A0-D9A6DADD8FAD}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5779,38 +5782,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="29" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="35" t="s">
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -5849,10 +5852,10 @@
       <c r="L2" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="32" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="23" t="s">
@@ -5885,10 +5888,10 @@
       <c r="X2" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="37" t="s">
+      <c r="Y2" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="33" t="s">
         <v>60</v>
       </c>
       <c r="AA2" s="27" t="s">
@@ -12517,11 +12520,11 @@
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X39 X41:X49 X61:X69 X71:X79 X51:X59 R101:R108 X81:X89 X91:X99 X12:X19 X3:X10 L21:L29 L31:L39 F41:F49 L61:L69 L71:L79 L51:L59 L101:L108 L81:L89 L91:L99 F12:F19 L3:L10 R21:R29 R31:R39 R41:R49 R61:R69 R71:R79 R51:R59 X101:X108 R81:R89 R91:R99 R12:R19 R3:R10 L12:L19 F71:F79 F21:F29 F61:F69 L41:L49 F51:F59 F3:F10 F81:F89 F91:F99 F101:F108 F31:F39" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S101:S108 Y101:Y108 G101:G108 Y3:Y10 S3:S10 M3:M10 G3:G10 M101:M108 Y12:Y19 S12:S19 G12:G19 M21:M29 M12:M19 Y21:Y29 S21:S29 S31:S39 M31:M39 G31:G39 Y31:Y39 Y41:Y49 S41:S49 G41:G49 G21:G29 G51:G59 Y51:Y59 S51:S59 M51:M59 M61:M69 G61:G69 Y61:Y69 S61:S69 S71:S79 M71:M79 M41:M49 Y71:Y79 Y81:Y89 S81:S89 M81:M89 G81:G89 G91:G99 Y91:Y99 S91:S99 M91:M99 G71:G79" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F91:F99 F101:F108 L3:L10 L12:L19 L21:L29 L31:L39 L41:L49 L51:L59 L61:L69 L71:L79 L81:L89 L91:L99 L101:L108 R3:R10 R12:R19 R21:R29 R31:R39 R41:R49 R51:R59 R61:R69 R71:R79 R81:R89 R91:R99 R101:R108 X3:X10 X12:X19 X21:X29 X31:X39 X41:X49 X51:X59 X61:X69 X71:X79 X81:X89 X91:X99 X100:X108" xr:uid="{376BEA66-08F1-46D4-BA3B-90F03F023D82}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12564,38 +12567,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="29" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="35" t="s">
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -12634,10 +12637,10 @@
       <c r="L2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="32" t="s">
         <v>73</v>
       </c>
       <c r="O2" s="23" t="s">
@@ -12670,10 +12673,10 @@
       <c r="X2" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="Y2" s="37" t="s">
+      <c r="Y2" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="33" t="s">
         <v>85</v>
       </c>
       <c r="AA2" s="27" t="s">
